--- a/剧情配置/事件与节点配置表_已解析.xlsx
+++ b/剧情配置/事件与节点配置表_已解析.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="79">
   <si>
     <t>中文名</t>
   </si>
@@ -218,15 +218,6 @@
   </si>
   <si>
     <t>权重</t>
-  </si>
-  <si>
-    <t>条件JSON</t>
-  </si>
-  <si>
-    <t>消耗JSON</t>
-  </si>
-  <si>
-    <t>效果JSON</t>
   </si>
   <si>
     <t>目标中文名</t>
@@ -1015,13 +1006,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="11" width="13" customWidth="1"/>
+    <col min="1" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>62</v>
       </c>
@@ -1046,17 +1037,8 @@
       <c r="H1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1067,7 +1049,7 @@
         <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -1076,22 +1058,13 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1102,7 +1075,7 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>31</v>
@@ -1111,22 +1084,13 @@
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1134,10 +1098,10 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
@@ -1146,22 +1110,13 @@
         <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1169,10 +1124,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -1181,22 +1136,13 @@
         <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -1204,10 +1150,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -1216,22 +1162,13 @@
         <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -1239,10 +1176,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -1251,22 +1188,13 @@
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -1274,10 +1202,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>
@@ -1286,18 +1214,9 @@
         <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1318,18 +1237,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
